--- a/database/event/3247/event_3247_evp_summary.xlsx
+++ b/database/event/3247/event_3247_evp_summary.xlsx
@@ -492,231 +492,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2718</v>
+        <v>6.7901</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7373</v>
+        <v>4.0461</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1123</v>
+        <v>2.2613</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2718</v>
+        <v>6.7901</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2264</v>
+        <v>2.579</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0454</v>
+        <v>4.2111</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2264</v>
+        <v>2.579</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2264</v>
+        <v>2.579</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0454</v>
+        <v>4.2111</v>
       </c>
       <c r="K2" t="n">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="L2" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2718</v>
+        <v>6.790100000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>276</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2357</v>
+        <v>6.7869</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7158</v>
+        <v>4.0442</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0977</v>
+        <v>2.26</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2357</v>
+        <v>6.7869</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0246</v>
+        <v>2.7415</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2111</v>
+        <v>4.0454</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0246</v>
+        <v>2.7415</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0246</v>
+        <v>2.7415</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2111</v>
+        <v>4.0454</v>
       </c>
       <c r="K3" t="n">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="L3" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2357</v>
+        <v>6.786899999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>330</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8443</v>
+        <v>6.4045</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4825</v>
+        <v>3.8163</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9396</v>
+        <v>2.1076</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8443</v>
+        <v>6.4045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8854</v>
+        <v>3.601</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9589</v>
+        <v>2.8035</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8854</v>
+        <v>3.601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8854</v>
+        <v>3.601</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9589</v>
+        <v>2.8035</v>
       </c>
       <c r="K4" t="n">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="L4" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8443</v>
+        <v>6.404500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>330</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1846</v>
+        <v>6.1762</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0894</v>
+        <v>3.6803</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6731</v>
+        <v>2.0167</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1846</v>
+        <v>6.1762</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5185</v>
+        <v>3.624</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6661</v>
+        <v>2.5522</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5185</v>
+        <v>3.624</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5185</v>
+        <v>3.624</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6661</v>
+        <v>2.5522</v>
       </c>
       <c r="K5" t="n">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>212</v>
+        <v>91</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1846</v>
+        <v>6.1762</v>
       </c>
       <c r="N5" t="n">
-        <v>330</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0991</v>
+        <v>5.9751</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0385</v>
+        <v>3.5605</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6386</v>
+        <v>1.9366</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0991</v>
+        <v>5.9751</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2956</v>
+        <v>1.0162</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8035</v>
+        <v>4.9589</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2956</v>
+        <v>1.0162</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2956</v>
+        <v>1.0162</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8035</v>
+        <v>4.9589</v>
       </c>
       <c r="K6" t="n">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="L6" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M6" t="n">
-        <v>5.0991</v>
+        <v>5.975099999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>276</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0282</v>
+        <v>5.8644</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9962</v>
+        <v>3.4945</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6099</v>
+        <v>1.8925</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0282</v>
+        <v>5.8644</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2497</v>
+        <v>3.0859</v>
       </c>
       <c r="G7" t="n">
         <v>2.7785</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2497</v>
+        <v>3.0859</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2497</v>
+        <v>3.0859</v>
       </c>
       <c r="J7" t="n">
         <v>2.7785</v>
@@ -759,7 +759,7 @@
         <v>205</v>
       </c>
       <c r="M7" t="n">
-        <v>5.0282</v>
+        <v>5.8644</v>
       </c>
       <c r="N7" t="n">
         <v>276</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5932</v>
+        <v>5.6924</v>
       </c>
       <c r="C8" t="n">
-        <v>2.737</v>
+        <v>3.392</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4342</v>
+        <v>1.8239</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5932</v>
+        <v>5.6924</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3442</v>
+        <v>2.7587</v>
       </c>
       <c r="G8" t="n">
-        <v>2.249</v>
+        <v>2.9337</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3442</v>
+        <v>2.7587</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3442</v>
+        <v>2.7587</v>
       </c>
       <c r="J8" t="n">
-        <v>2.249</v>
+        <v>2.9337</v>
       </c>
       <c r="K8" t="n">
         <v>118</v>
@@ -805,7 +805,7 @@
         <v>212</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5932</v>
+        <v>5.6924</v>
       </c>
       <c r="N8" t="n">
         <v>330</v>
@@ -814,81 +814,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4708</v>
+        <v>5.5814</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6641</v>
+        <v>3.3259</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3847</v>
+        <v>1.7797</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4708</v>
+        <v>5.5814</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9186</v>
+        <v>1.9153</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5522</v>
+        <v>3.6661</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9186</v>
+        <v>1.9153</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9186</v>
+        <v>1.9153</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5522</v>
+        <v>3.6661</v>
       </c>
       <c r="K9" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="L9" t="n">
-        <v>91</v>
+        <v>212</v>
       </c>
       <c r="M9" t="n">
-        <v>4.470800000000001</v>
+        <v>5.5814</v>
       </c>
       <c r="N9" t="n">
-        <v>177</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.4023</v>
+        <v>5.5584</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6233</v>
+        <v>3.3122</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3571</v>
+        <v>1.7706</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4023</v>
+        <v>5.5584</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4686</v>
+        <v>3.3094</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9337</v>
+        <v>2.249</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4686</v>
+        <v>3.3094</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4686</v>
+        <v>3.3094</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9337</v>
+        <v>2.249</v>
       </c>
       <c r="K10" t="n">
         <v>118</v>
@@ -897,7 +897,7 @@
         <v>212</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4023</v>
+        <v>5.558400000000001</v>
       </c>
       <c r="N10" t="n">
         <v>330</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2538</v>
+        <v>4.6691</v>
       </c>
       <c r="C11" t="n">
-        <v>2.5348</v>
+        <v>2.7822</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2971</v>
+        <v>1.4163</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2538</v>
+        <v>4.6691</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8847</v>
+        <v>4.3961</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3691</v>
+        <v>0.273</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8847</v>
+        <v>4.59</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8847</v>
+        <v>4.59</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3691</v>
+        <v>0.273</v>
       </c>
       <c r="K11" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="L11" t="n">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2538</v>
+        <v>4.863</v>
       </c>
       <c r="N11" t="n">
-        <v>276</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4271</v>
+        <v>4.4586</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0422</v>
+        <v>2.6568</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9631</v>
+        <v>1.3324</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4271</v>
+        <v>4.4586</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6511</v>
+        <v>3.6826</v>
       </c>
       <c r="G12" t="n">
         <v>0.776</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6511</v>
+        <v>3.6826</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6511</v>
+        <v>3.6826</v>
       </c>
       <c r="J12" t="n">
         <v>0.776</v>
@@ -989,7 +989,7 @@
         <v>91</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4271</v>
+        <v>4.4586</v>
       </c>
       <c r="N12" t="n">
         <v>177</v>
@@ -998,81 +998,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6466</v>
+        <v>4.4285</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5771</v>
+        <v>2.6389</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6478</v>
+        <v>1.3204</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6466</v>
+        <v>4.4285</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3736</v>
+        <v>1.0594</v>
       </c>
       <c r="G13" t="n">
-        <v>0.273</v>
+        <v>3.3691</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3736</v>
+        <v>1.0594</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3736</v>
+        <v>1.0594</v>
       </c>
       <c r="J13" t="n">
-        <v>0.273</v>
+        <v>3.3691</v>
       </c>
       <c r="K13" t="n">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="L13" t="n">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6466</v>
+        <v>4.4285</v>
       </c>
       <c r="N13" t="n">
-        <v>210</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.537</v>
+        <v>3.7684</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5118</v>
+        <v>2.2455</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6035</v>
+        <v>1.0574</v>
       </c>
       <c r="E14" t="n">
-        <v>2.537</v>
+        <v>3.7684</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1311</v>
+        <v>4.6552</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4059</v>
+        <v>-0.8868</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1311</v>
+        <v>4.9962</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1311</v>
+        <v>4.9962</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4059</v>
+        <v>-0.8868</v>
       </c>
       <c r="K14" t="n">
         <v>124</v>
@@ -1081,7 +1081,7 @@
         <v>60</v>
       </c>
       <c r="M14" t="n">
-        <v>2.537</v>
+        <v>4.1094</v>
       </c>
       <c r="N14" t="n">
         <v>184</v>
@@ -1090,1366 +1090,1366 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3202</v>
+        <v>3.6021</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3826</v>
+        <v>2.1464</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5159</v>
+        <v>0.9912</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3202</v>
+        <v>3.6021</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3293</v>
+        <v>2.3853</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9909</v>
+        <v>1.2168</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3293</v>
+        <v>2.3853</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3293</v>
+        <v>2.3853</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9909</v>
+        <v>1.2168</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="L15" t="n">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3202</v>
+        <v>3.6021</v>
       </c>
       <c r="N15" t="n">
-        <v>278</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1987</v>
+        <v>3.3645</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3102</v>
+        <v>2.0049</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4669</v>
+        <v>0.8965</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1987</v>
+        <v>3.3645</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9819</v>
+        <v>2.3736</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2168</v>
+        <v>0.9909</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9819</v>
+        <v>2.3736</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9819</v>
+        <v>2.3736</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2168</v>
+        <v>0.9909</v>
       </c>
       <c r="K16" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="L16" t="n">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1987</v>
+        <v>3.3645</v>
       </c>
       <c r="N16" t="n">
-        <v>177</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1731</v>
+        <v>2.8662</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2949</v>
+        <v>1.7079</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4565</v>
+        <v>0.698</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1731</v>
+        <v>2.8662</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8835</v>
+        <v>2.4603</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2896</v>
+        <v>0.4059</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8835</v>
+        <v>2.4603</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8835</v>
+        <v>2.4603</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2896</v>
+        <v>0.4059</v>
       </c>
       <c r="K17" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1731</v>
+        <v>2.8662</v>
       </c>
       <c r="N17" t="n">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9838</v>
+        <v>2.8239</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1821</v>
+        <v>1.6827</v>
       </c>
       <c r="D18" t="n">
-        <v>0.38</v>
+        <v>0.6811</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9838</v>
+        <v>2.8239</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7067</v>
+        <v>2.8239</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2771</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7067</v>
+        <v>2.8239</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7067</v>
+        <v>2.8239</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2771</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9838</v>
+        <v>2.8239</v>
       </c>
       <c r="N18" t="n">
-        <v>210</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9436</v>
+        <v>2.8168</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1582</v>
+        <v>1.6785</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3638</v>
+        <v>0.6783</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9436</v>
+        <v>2.8168</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3067</v>
+        <v>1.5397</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6369</v>
+        <v>1.2771</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3067</v>
+        <v>1.5397</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3067</v>
+        <v>1.5397</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6369</v>
+        <v>1.2771</v>
       </c>
       <c r="K19" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="L19" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9436</v>
+        <v>2.8168</v>
       </c>
       <c r="N19" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.858</v>
+        <v>2.5007</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1072</v>
+        <v>1.4901</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3292</v>
+        <v>0.5524</v>
       </c>
       <c r="E20" t="n">
-        <v>1.858</v>
+        <v>2.5007</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6604</v>
+        <v>2.2111</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1976</v>
+        <v>0.2896</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6604</v>
+        <v>2.2111</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6604</v>
+        <v>2.2111</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1976</v>
+        <v>0.2896</v>
       </c>
       <c r="K20" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L20" t="n">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>1.858</v>
+        <v>2.5007</v>
       </c>
       <c r="N20" t="n">
-        <v>177</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6452</v>
+        <v>2.4545</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9804</v>
+        <v>1.4626</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2433</v>
+        <v>0.534</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6452</v>
+        <v>2.4545</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6452</v>
+        <v>2.2569</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.1976</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6452</v>
+        <v>2.2569</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6452</v>
+        <v>2.2569</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.1976</v>
       </c>
       <c r="K21" t="n">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6452</v>
+        <v>2.4545</v>
       </c>
       <c r="N21" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4799</v>
+        <v>2.4368</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8819</v>
+        <v>1.4521</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1765</v>
+        <v>0.5269</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4799</v>
+        <v>2.4368</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0426</v>
+        <v>1.7999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5627</v>
+        <v>0.6369</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0426</v>
+        <v>1.7999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0426</v>
+        <v>1.7999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5627</v>
+        <v>0.6369</v>
       </c>
       <c r="K22" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="L22" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4799</v>
+        <v>2.4368</v>
       </c>
       <c r="N22" t="n">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4611</v>
+        <v>2.4329</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8706</v>
+        <v>1.4497</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1689</v>
+        <v>0.5254</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4611</v>
+        <v>2.4329</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3479</v>
+        <v>3.4329</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8868</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3479</v>
+        <v>3.4329</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3479</v>
+        <v>3.4329</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8868</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="L23" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4611</v>
+        <v>2.4329</v>
       </c>
       <c r="N23" t="n">
-        <v>184</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.383</v>
+        <v>2.2567</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8241000000000001</v>
+        <v>1.3447</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1373</v>
+        <v>0.4552</v>
       </c>
       <c r="E24" t="n">
-        <v>1.383</v>
+        <v>2.2567</v>
       </c>
       <c r="F24" t="n">
-        <v>1.383</v>
+        <v>2.4635</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.2068</v>
       </c>
       <c r="H24" t="n">
-        <v>1.383</v>
+        <v>2.4635</v>
       </c>
       <c r="I24" t="n">
-        <v>1.383</v>
+        <v>2.4635</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.2068</v>
       </c>
       <c r="K24" t="n">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M24" t="n">
-        <v>1.383</v>
+        <v>2.2567</v>
       </c>
       <c r="N24" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3493</v>
+        <v>2.1314</v>
       </c>
       <c r="C25" t="n">
-        <v>0.804</v>
+        <v>1.2701</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1237</v>
+        <v>0.4052</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3493</v>
+        <v>2.1314</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3493</v>
+        <v>2.1314</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3493</v>
+        <v>2.1314</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3493</v>
+        <v>2.1314</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="L25" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3493</v>
+        <v>2.1314</v>
       </c>
       <c r="N25" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1861</v>
+        <v>2.0342</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7068</v>
+        <v>1.2122</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0578</v>
+        <v>0.3665</v>
       </c>
       <c r="E26" t="n">
-        <v>1.1861</v>
+        <v>2.0342</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1861</v>
+        <v>2.5969</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.5627</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1861</v>
+        <v>2.5969</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1861</v>
+        <v>2.5969</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.5627</v>
       </c>
       <c r="K26" t="n">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1861</v>
+        <v>2.0342</v>
       </c>
       <c r="N26" t="n">
-        <v>140</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.186</v>
+        <v>1.5257</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7067</v>
+        <v>0.9091</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0578</v>
+        <v>0.1639</v>
       </c>
       <c r="E27" t="n">
-        <v>1.186</v>
+        <v>1.5257</v>
       </c>
       <c r="F27" t="n">
-        <v>1.186</v>
+        <v>1.5257</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.186</v>
+        <v>1.5257</v>
       </c>
       <c r="I27" t="n">
-        <v>1.186</v>
+        <v>1.5257</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.186</v>
+        <v>1.5257</v>
       </c>
       <c r="N27" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>waterfaLLZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1119</v>
+        <v>1.5131</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6626</v>
+        <v>0.9016</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0278</v>
+        <v>0.1589</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1119</v>
+        <v>1.5131</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1119</v>
+        <v>2.3066</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.7935</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1119</v>
+        <v>2.3066</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1119</v>
+        <v>2.3066</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.7935</v>
       </c>
       <c r="K28" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1119</v>
+        <v>1.5131</v>
       </c>
       <c r="N28" t="n">
-        <v>98</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0479</v>
+        <v>1.4234</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6244</v>
+        <v>0.8482</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002</v>
+        <v>0.1232</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0479</v>
+        <v>1.4234</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0479</v>
+        <v>1.4234</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0479</v>
+        <v>1.4234</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0479</v>
+        <v>1.4234</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0479</v>
+        <v>1.4234</v>
       </c>
       <c r="N29" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>waterfaLLZ</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0442</v>
+        <v>1.4167</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6222</v>
+        <v>0.8442</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0005</v>
+        <v>0.1205</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0442</v>
+        <v>1.4167</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8377</v>
+        <v>1.4167</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7935</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8377</v>
+        <v>1.4167</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8377</v>
+        <v>1.4167</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7935</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0442</v>
+        <v>1.4167</v>
       </c>
       <c r="N30" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8045</v>
+        <v>1.3915</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4794</v>
+        <v>0.8292</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0964</v>
+        <v>0.1105</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8045</v>
+        <v>1.3915</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5888</v>
+        <v>1.4093</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2157</v>
+        <v>-0.0178</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5888</v>
+        <v>1.4093</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5888</v>
+        <v>1.4093</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2157</v>
+        <v>-0.0178</v>
       </c>
       <c r="K31" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="L31" t="n">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8045</v>
+        <v>1.3915</v>
       </c>
       <c r="N31" t="n">
-        <v>278</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7364000000000001</v>
+        <v>1.2447</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4388</v>
+        <v>0.7417</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1239</v>
+        <v>0.052</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7364000000000001</v>
+        <v>1.2447</v>
       </c>
       <c r="F32" t="n">
-        <v>0.463</v>
+        <v>1.2447</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2734</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.463</v>
+        <v>1.2447</v>
       </c>
       <c r="I32" t="n">
-        <v>0.463</v>
+        <v>1.2447</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2734</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="L32" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7363999999999999</v>
+        <v>1.2447</v>
       </c>
       <c r="N32" t="n">
-        <v>210</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5264</v>
+        <v>1.2023</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3137</v>
+        <v>0.7164</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2087</v>
+        <v>0.0351</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5264</v>
+        <v>1.2023</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5264</v>
+        <v>1.2023</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5264</v>
+        <v>1.2023</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5264</v>
+        <v>1.2023</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5264</v>
+        <v>1.2023</v>
       </c>
       <c r="N33" t="n">
-        <v>98</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5139</v>
+        <v>1.1053</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3062</v>
+        <v>0.6586</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2138</v>
+        <v>-0.0036</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5139</v>
+        <v>1.1053</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5139</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.2157</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5139</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5139</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.2157</v>
       </c>
       <c r="K34" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5139</v>
+        <v>1.1053</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4924</v>
+        <v>1.0479</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2934</v>
+        <v>0.6244</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2224</v>
+        <v>-0.0264</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4924</v>
+        <v>1.0479</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5102</v>
+        <v>1.0479</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0178</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5102</v>
+        <v>1.0479</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5102</v>
+        <v>1.0479</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0178</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="L35" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4924</v>
+        <v>1.0479</v>
       </c>
       <c r="N35" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Kvik</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.444</v>
+        <v>0.9216</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2646</v>
+        <v>0.5492</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.242</v>
+        <v>-0.0767</v>
       </c>
       <c r="E36" t="n">
-        <v>0.444</v>
+        <v>0.9216</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6508</v>
+        <v>1.4659</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2068</v>
+        <v>-0.5443</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6508</v>
+        <v>1.4659</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6508</v>
+        <v>1.4659</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2068</v>
+        <v>-0.5443</v>
       </c>
       <c r="K36" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L36" t="n">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4440000000000001</v>
+        <v>0.9216</v>
       </c>
       <c r="N36" t="n">
-        <v>210</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3354</v>
+        <v>0.907</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1999</v>
+        <v>0.5405</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2859</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3354</v>
+        <v>0.907</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9982</v>
+        <v>0.907</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6627999999999999</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9982</v>
+        <v>0.907</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9982</v>
+        <v>0.907</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6627999999999999</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="L37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3354</v>
+        <v>0.907</v>
       </c>
       <c r="N37" t="n">
-        <v>184</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3164</v>
+        <v>0.7799</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1885</v>
+        <v>0.4647</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2935</v>
+        <v>-0.1332</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3164</v>
+        <v>0.7799</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0566</v>
+        <v>0.5065</v>
       </c>
       <c r="G38" t="n">
-        <v>0.373</v>
+        <v>0.2734</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0566</v>
+        <v>0.5065</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0566</v>
+        <v>0.5065</v>
       </c>
       <c r="J38" t="n">
-        <v>0.373</v>
+        <v>0.2734</v>
       </c>
       <c r="K38" t="n">
         <v>111</v>
       </c>
       <c r="L38" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3164</v>
+        <v>0.7798999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>278</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3147</v>
+        <v>0.5611</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1875</v>
+        <v>0.3344</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2942</v>
+        <v>-0.2204</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3147</v>
+        <v>0.5611</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3147</v>
+        <v>0.5611</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147</v>
+        <v>0.5611</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3147</v>
+        <v>0.5611</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3147</v>
+        <v>0.5611</v>
       </c>
       <c r="N39" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2144</v>
+        <v>0.5139</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1278</v>
+        <v>0.3062</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3347</v>
+        <v>-0.2392</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2144</v>
+        <v>0.5139</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2144</v>
+        <v>0.5139</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2144</v>
+        <v>0.5139</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2144</v>
+        <v>0.5139</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2144</v>
+        <v>0.5139</v>
       </c>
       <c r="N40" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2129</v>
+        <v>0.4938</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1269</v>
+        <v>0.2942</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3354</v>
+        <v>-0.2472</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2129</v>
+        <v>0.4938</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2129</v>
+        <v>1.1566</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2129</v>
+        <v>1.1566</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2129</v>
+        <v>1.1566</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2129</v>
+        <v>0.4938000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>90</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0147</v>
+        <v>0.4601</v>
       </c>
       <c r="C42" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.2742</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4154</v>
+        <v>-0.2606</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0147</v>
+        <v>0.4601</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0147</v>
+        <v>0.0871</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0147</v>
+        <v>0.0871</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0147</v>
+        <v>0.0871</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="K42" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0147</v>
+        <v>0.4601</v>
       </c>
       <c r="N42" t="n">
-        <v>94</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.0617</v>
+        <v>0.4257</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0368</v>
+        <v>0.2537</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4463</v>
+        <v>-0.2743</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0617</v>
+        <v>0.4257</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.0617</v>
+        <v>0.4257</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.0617</v>
+        <v>0.4257</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0617</v>
+        <v>0.4257</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0617</v>
+        <v>0.4257</v>
       </c>
       <c r="N43" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.0735</v>
+        <v>0.2144</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0438</v>
+        <v>0.1278</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4511</v>
+        <v>-0.3585</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0735</v>
+        <v>0.2144</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.0735</v>
+        <v>0.2144</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.0735</v>
+        <v>0.2144</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0735</v>
+        <v>0.2144</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0735</v>
+        <v>0.2144</v>
       </c>
       <c r="N44" t="n">
         <v>84</v>
@@ -2470,185 +2470,185 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>hutji</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1188</v>
+        <v>0.2056</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0708</v>
+        <v>0.1225</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4694</v>
+        <v>-0.362</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.1188</v>
+        <v>0.2056</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1188</v>
+        <v>0.2056</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1188</v>
+        <v>0.2056</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1188</v>
+        <v>0.2056</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.1188</v>
+        <v>0.2056</v>
       </c>
       <c r="N45" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kvik</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.3456</v>
+        <v>-0.0617</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2059</v>
+        <v>-0.0368</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.4685</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.3456</v>
+        <v>-0.0617</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1987</v>
+        <v>-0.0617</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1987</v>
+        <v>-0.0617</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1987</v>
+        <v>-0.0617</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="L46" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.3456</v>
+        <v>-0.0617</v>
       </c>
       <c r="N46" t="n">
-        <v>147</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.349</v>
+        <v>-0.0735</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.208</v>
+        <v>-0.0438</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5624</v>
+        <v>-0.4732</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.349</v>
+        <v>-0.0735</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4656</v>
+        <v>-0.0735</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.8146</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4656</v>
+        <v>-0.0735</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4656</v>
+        <v>-0.0735</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8146</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L47" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.349</v>
+        <v>-0.0735</v>
       </c>
       <c r="N47" t="n">
-        <v>278</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hutji</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.36</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2145</v>
+        <v>-0.0466</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5668</v>
+        <v>-0.4751</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.36</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.36</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.8146</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.36</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.36</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.8146</v>
       </c>
       <c r="K48" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.36</v>
+        <v>-0.07819999999999994</v>
       </c>
       <c r="N48" t="n">
-        <v>112</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49">
@@ -2664,7 +2664,7 @@
         <v>-0.227</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5752</v>
+        <v>-0.5957</v>
       </c>
       <c r="E49" t="n">
         <v>-0.3809</v>
@@ -2710,7 +2710,7 @@
         <v>-0.2363</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5816</v>
+        <v>-0.6019</v>
       </c>
       <c r="E50" t="n">
         <v>-0.3966</v>
@@ -2746,78 +2746,78 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.4455</v>
+        <v>-0.4137</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2655</v>
+        <v>-0.2465</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.6087</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4455</v>
+        <v>-0.4137</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4455</v>
+        <v>0.5863</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4455</v>
+        <v>0.5863</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4455</v>
+        <v>0.5863</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K51" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.4455</v>
+        <v>-0.4137</v>
       </c>
       <c r="N51" t="n">
-        <v>94</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5148</v>
+        <v>-0.4455</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3068</v>
+        <v>-0.2655</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6293</v>
+        <v>-0.6214</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5148</v>
+        <v>-0.4455</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.5148</v>
+        <v>-0.4455</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5148</v>
+        <v>-0.4455</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.5148</v>
+        <v>-0.4455</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5148</v>
+        <v>-0.4455</v>
       </c>
       <c r="N52" t="n">
         <v>94</v>
@@ -2838,538 +2838,538 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.5194</v>
+        <v>-0.5148</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3095</v>
+        <v>-0.3068</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6312</v>
+        <v>-0.649</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5194</v>
+        <v>-0.5148</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.5194</v>
+        <v>-0.5148</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5194</v>
+        <v>-0.5148</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5194</v>
+        <v>-0.5148</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.5194</v>
+        <v>-0.5148</v>
       </c>
       <c r="N53" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.5501</v>
+        <v>-0.5194</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.3278</v>
+        <v>-0.3095</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.6508</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5501</v>
+        <v>-0.5194</v>
       </c>
       <c r="F54" t="n">
-        <v>0.001</v>
+        <v>-0.5194</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.5511</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.001</v>
+        <v>-0.5194</v>
       </c>
       <c r="I54" t="n">
-        <v>0.001</v>
+        <v>-0.5194</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.5511</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="L54" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.5501</v>
+        <v>-0.5194</v>
       </c>
       <c r="N54" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.6562</v>
+        <v>-0.55</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.391</v>
+        <v>-0.3277</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6865</v>
+        <v>-0.663</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.6562</v>
+        <v>-0.55</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.6562</v>
+        <v>0.0011</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.5511</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.6562</v>
+        <v>0.0011</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6562</v>
+        <v>0.0011</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.5511</v>
       </c>
       <c r="K55" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.6562</v>
+        <v>-0.55</v>
       </c>
       <c r="N55" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.5598</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4671</v>
+        <v>-0.3336</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.738</v>
+        <v>-0.6669</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.5598</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2702</v>
+        <v>-0.5598</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2702</v>
+        <v>-0.5598</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2702</v>
+        <v>-0.5598</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L56" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.7837999999999999</v>
+        <v>-0.5598</v>
       </c>
       <c r="N56" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.8166</v>
+        <v>-0.7605</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4866</v>
+        <v>-0.4532</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7513</v>
+        <v>-0.7469</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.8166</v>
+        <v>-0.7605</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5164</v>
+        <v>-0.2469</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.3002</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5164</v>
+        <v>-0.2469</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.5164</v>
+        <v>-0.2469</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.3002</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L57" t="n">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.8166</v>
+        <v>-0.7605</v>
       </c>
       <c r="N57" t="n">
-        <v>278</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>keshandr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.8495</v>
+        <v>-0.8159</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.5062</v>
+        <v>-0.4862</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7645</v>
+        <v>-0.769</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.8495</v>
+        <v>-0.8159</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.8159</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.3016</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.8159</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.8159</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.3016</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L58" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.8495</v>
+        <v>-0.8159</v>
       </c>
       <c r="N58" t="n">
-        <v>210</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.8958</v>
+        <v>-0.8166</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.4866</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7832</v>
+        <v>-0.7692</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.8958</v>
+        <v>-0.8166</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8958</v>
+        <v>-0.5164</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.3002</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.8958</v>
+        <v>-0.5164</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.8958</v>
+        <v>-0.5164</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.3002</v>
       </c>
       <c r="K59" t="n">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.8958</v>
+        <v>-0.8166</v>
       </c>
       <c r="N59" t="n">
-        <v>64</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.9244</v>
+        <v>-0.8459</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5508</v>
+        <v>-0.5041</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7948</v>
+        <v>-0.7809</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.9244</v>
+        <v>-0.8459</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.9244</v>
+        <v>-0.5443</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0.3016</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.9244</v>
+        <v>-0.5443</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.9244</v>
+        <v>-0.5443</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-0.3016</v>
       </c>
       <c r="K60" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.9244</v>
+        <v>-0.8459</v>
       </c>
       <c r="N60" t="n">
-        <v>129</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>keshandr</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.9425</v>
+        <v>-0.8958</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.5616</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8021</v>
+        <v>-0.8008</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.9425</v>
+        <v>-0.8958</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.9425</v>
+        <v>-0.8958</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.9425</v>
+        <v>-0.8958</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9425</v>
+        <v>-0.8958</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.9425</v>
+        <v>-0.8958</v>
       </c>
       <c r="N61" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.9821</v>
+        <v>-0.9244</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5508</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8181</v>
+        <v>-0.8122</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.9821</v>
+        <v>-0.9244</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.9821</v>
+        <v>-0.9244</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.9821</v>
+        <v>-0.9244</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.9821</v>
+        <v>-0.9244</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.9821</v>
+        <v>-0.9244</v>
       </c>
       <c r="N62" t="n">
-        <v>64</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>balblna</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1373</v>
+        <v>-0.9742</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.6777</v>
+        <v>-0.5805</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8808</v>
+        <v>-0.832</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.1373</v>
+        <v>-0.9742</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.1373</v>
+        <v>0.0258</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.1373</v>
+        <v>0.0258</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.1373</v>
+        <v>0.0258</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K63" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M63" t="n">
-        <v>-1.1373</v>
+        <v>-0.9742</v>
       </c>
       <c r="N63" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1395</v>
+        <v>-0.9821</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.679</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8817</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.1395</v>
+        <v>-0.9821</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.1395</v>
+        <v>-0.9821</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.1395</v>
+        <v>-0.9821</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.1395</v>
+        <v>-0.9821</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-1.1395</v>
+        <v>-0.9821</v>
       </c>
       <c r="N64" t="n">
         <v>64</v>
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1976</v>
+        <v>-1.0189</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.7136</v>
+        <v>-0.6071</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9052</v>
+        <v>-0.8498</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.1976</v>
+        <v>-1.0189</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.1976</v>
+        <v>-1.0189</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.1976</v>
+        <v>-1.0189</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.1976</v>
+        <v>-1.0189</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.1976</v>
+        <v>-1.0189</v>
       </c>
       <c r="N65" t="n">
         <v>90</v>
@@ -3436,124 +3436,124 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>jmqa</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.2314</v>
+        <v>-1.0837</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.7338</v>
+        <v>-0.6458</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9188</v>
+        <v>-0.8757</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.2314</v>
+        <v>-1.0837</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.2314</v>
+        <v>-0.0837</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.2314</v>
+        <v>-0.0837</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.2314</v>
+        <v>-0.0837</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K66" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.2314</v>
+        <v>-1.0837</v>
       </c>
       <c r="N66" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>balblna</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.2394</v>
+        <v>-1.1373</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.7385</v>
+        <v>-0.6777</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9221</v>
+        <v>-0.897</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2394</v>
+        <v>-1.1373</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2394</v>
+        <v>-1.1373</v>
       </c>
       <c r="G67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2394</v>
+        <v>-1.1373</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2394</v>
+        <v>-1.1373</v>
       </c>
       <c r="J67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="L67" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.2394</v>
+        <v>-1.1373</v>
       </c>
       <c r="N67" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2678</v>
+        <v>-1.1395</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.679</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9335</v>
+        <v>-0.8979</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2678</v>
+        <v>-1.1395</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.2678</v>
+        <v>-1.1395</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.2678</v>
+        <v>-1.1395</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.2678</v>
+        <v>-1.1395</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.2678</v>
+        <v>-1.1395</v>
       </c>
       <c r="N68" t="n">
         <v>64</v>
@@ -3574,93 +3574,93 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jmqa</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2689</v>
+        <v>-1.2314</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7561</v>
+        <v>-0.7338</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9345</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2689</v>
+        <v>-1.2314</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2689</v>
+        <v>-1.2314</v>
       </c>
       <c r="G69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2689</v>
+        <v>-1.2314</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2689</v>
+        <v>-1.2314</v>
       </c>
       <c r="J69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="L69" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.2689</v>
+        <v>-1.2314</v>
       </c>
       <c r="N69" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2795</v>
+        <v>-1.2678</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.7624</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9383</v>
+        <v>-0.949</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2795</v>
+        <v>-1.2678</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.2795</v>
+        <v>-1.2678</v>
       </c>
       <c r="G70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.2795</v>
+        <v>-1.2678</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2795</v>
+        <v>-1.2678</v>
       </c>
       <c r="J70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="L70" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2795</v>
+        <v>-1.2678</v>
       </c>
       <c r="N70" t="n">
-        <v>184</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71">
@@ -3676,7 +3676,7 @@
         <v>-0.7727000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9452</v>
+        <v>-0.9605</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2967</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7902</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9571</v>
+        <v>-0.9722</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3261</v>
@@ -3758,93 +3758,93 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>jR</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.362</v>
+        <v>-1.3378</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.8116</v>
+        <v>-0.7972</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9716</v>
+        <v>-0.9769</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.362</v>
+        <v>-1.3378</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.362</v>
+        <v>-1.3378</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.362</v>
+        <v>-1.3378</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.362</v>
+        <v>-1.3378</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.362</v>
+        <v>-1.3378</v>
       </c>
       <c r="N73" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>zews</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.486</v>
+        <v>-1.362</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8855</v>
+        <v>-0.8116</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0217</v>
+        <v>-0.9865</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.486</v>
+        <v>-1.362</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.486</v>
+        <v>-1.362</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.486</v>
+        <v>-1.362</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.486</v>
+        <v>-1.362</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.486</v>
+        <v>-1.362</v>
       </c>
       <c r="N74" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.4968</v>
+        <v>-1.3843</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8919</v>
+        <v>-0.8249</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.026</v>
+        <v>-0.9954</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.4968</v>
+        <v>-1.3843</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.5465</v>
+        <v>-0.434</v>
       </c>
       <c r="G75" t="n">
         <v>-0.9503</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.5465</v>
+        <v>-0.434</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5465</v>
+        <v>-0.434</v>
       </c>
       <c r="J75" t="n">
         <v>-0.9503</v>
@@ -3887,7 +3887,7 @@
         <v>91</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.4968</v>
+        <v>-1.3843</v>
       </c>
       <c r="N75" t="n">
         <v>177</v>
@@ -3896,47 +3896,47 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jR</t>
+          <t>zews</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.6036</v>
+        <v>-1.486</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9556</v>
+        <v>-0.8855</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0692</v>
+        <v>-1.0359</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.6036</v>
+        <v>-1.486</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.6036</v>
+        <v>-1.486</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.6036</v>
+        <v>-1.486</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.6036</v>
+        <v>-1.486</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.6036</v>
+        <v>-1.486</v>
       </c>
       <c r="N76" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77">
@@ -3952,7 +3952,7 @@
         <v>-1.0872</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1584</v>
+        <v>-1.1708</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8245</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1039</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1697</v>
+        <v>-1.1819</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8525</v>
@@ -4044,7 +4044,7 @@
         <v>-1.1197</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1805</v>
+        <v>-1.1925</v>
       </c>
       <c r="E79" t="n">
         <v>-1.8791</v>
@@ -4090,7 +4090,7 @@
         <v>-1.4351</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3943</v>
+        <v>-1.4034</v>
       </c>
       <c r="E80" t="n">
         <v>-2.4083</v>
@@ -4136,7 +4136,7 @@
         <v>-1.5892</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4987</v>
+        <v>-1.5064</v>
       </c>
       <c r="E81" t="n">
         <v>-2.6669</v>
